--- a/kospi200.xlsx
+++ b/kospi200.xlsx
@@ -471,32 +471,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>290,000</t>
+          <t>291,750</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>하락 24,500</t>
+          <t>하락 22,750</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-7.79%</t>
+          <t>-7.23%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10,364,075</t>
+          <t>27,055,137</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3,025,287</t>
+          <t>7,961,397</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>16,954,208</t>
+          <t>17,056,518</t>
         </is>
       </c>
     </row>
@@ -513,32 +513,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2,317,000</t>
+          <t>2,326,000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>하락 243,000</t>
+          <t>하락 234,000</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-9.49%</t>
+          <t>-9.14%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1,550,756</t>
+          <t>4,445,312</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3,648,125</t>
+          <t>10,512,123</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>16,513,314</t>
+          <t>16,577,457</t>
         </is>
       </c>
     </row>
@@ -555,32 +555,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1,559,000</t>
+          <t>1,585,000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>하락 198,000</t>
+          <t>하락 172,000</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-11.27%</t>
+          <t>-9.79%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>306,964</t>
+          <t>1,014,525</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>486,019</t>
+          <t>1,628,912</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2,057,231</t>
+          <t>2,091,540</t>
         </is>
       </c>
     </row>
@@ -597,32 +597,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1,959,000</t>
+          <t>1,994,000</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>하락 246,000</t>
+          <t>하락 211,000</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-11.16%</t>
+          <t>-9.57%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>244,629</t>
+          <t>702,535</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>490,163</t>
+          <t>1,410,739</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1,463,250</t>
+          <t>1,489,392</t>
         </is>
       </c>
     </row>
@@ -639,32 +639,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>459,500</t>
+          <t>492,500</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>하락 28,000</t>
+          <t>상승 5,000</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-5.74%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>249,272</t>
+          <t>994,926</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>115,614</t>
+          <t>480,609</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>940,862</t>
+          <t>1,008,432</t>
         </is>
       </c>
     </row>
@@ -681,32 +681,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>349,000</t>
+          <t>359,000</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>상승 1,000</t>
+          <t>상승 11,000</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>+3.16%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>71,223</t>
+          <t>274,341</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>24,551</t>
+          <t>97,025</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>816,660</t>
+          <t>840,060</t>
         </is>
       </c>
     </row>
@@ -723,32 +723,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>362,000</t>
+          <t>374,000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>하락 25,000</t>
+          <t>하락 13,000</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-6.46%</t>
+          <t>-3.36%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>102,614</t>
+          <t>357,468</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>36,862</t>
+          <t>131,954</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>724,000</t>
+          <t>748,000</t>
         </is>
       </c>
     </row>
@@ -765,32 +765,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>401,500</t>
+          <t>414,000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>하락 32,500</t>
+          <t>하락 20,000</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-7.49%</t>
+          <t>-4.61%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>172,589</t>
+          <t>537,968</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>69,372</t>
+          <t>220,780</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>651,103</t>
+          <t>671,374</t>
         </is>
       </c>
     </row>
@@ -807,32 +807,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1,385,000</t>
+          <t>1,429,000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>하락 11,000</t>
+          <t>상승 33,000</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>8,718</t>
+          <t>49,899</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>11,988</t>
+          <t>70,773</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>641,130</t>
+          <t>661,498</t>
         </is>
       </c>
     </row>
@@ -849,32 +849,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>587,000</t>
+          <t>603,000</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>하락 28,000</t>
+          <t>하락 12,000</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-4.55%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>65,369</t>
+          <t>184,426</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>38,420</t>
+          <t>110,116</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>616,122</t>
+          <t>632,916</t>
         </is>
       </c>
     </row>
@@ -891,32 +891,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>164,300</t>
+          <t>169,300</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>상승 5,800</t>
+          <t>상승 10,800</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>+3.66%</t>
+          <t>+6.81%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>455,317</t>
+          <t>1,830,842</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>73,584</t>
+          <t>307,612</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>582,752</t>
+          <t>600,486</t>
         </is>
       </c>
     </row>
@@ -933,116 +933,116 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1,123,000</t>
+          <t>1,163,000</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>상승 32,000</t>
+          <t>상승 72,000</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>+2.93%</t>
+          <t>+6.60%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>89,671</t>
+          <t>281,989</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>101,258</t>
+          <t>325,436</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>579,057</t>
+          <t>599,682</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000270</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>84,600</t>
+          <t>147,800</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>하락 3,900</t>
+          <t>상승 6,300</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-4.41%</t>
+          <t>+4.45%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>672,717</t>
+          <t>924,484</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>57,448</t>
+          <t>133,117</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>541,915</t>
+          <t>577,030</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>000270</t>
+          <t>034020</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>138,400</t>
+          <t>87,800</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>하락 3,100</t>
+          <t>하락 700</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>216,233</t>
+          <t>2,002,730</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>30,175</t>
+          <t>173,726</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>540,332</t>
+          <t>562,413</t>
         </is>
       </c>
     </row>
@@ -1059,32 +1059,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>676,000</t>
+          <t>694,000</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>하락 87,000</t>
+          <t>하락 69,000</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-11.40%</t>
+          <t>-9.04%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>117,773</t>
+          <t>297,337</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>80,799</t>
+          <t>206,494</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>490,118</t>
+          <t>503,169</t>
         </is>
       </c>
     </row>
@@ -1101,32 +1101,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>98,900</t>
+          <t>103,600</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>상승 2,500</t>
+          <t>상승 7,200</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>+2.59%</t>
+          <t>+7.47%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>305,089</t>
+          <t>1,410,004</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>29,598</t>
+          <t>143,290</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>469,433</t>
+          <t>491,742</t>
         </is>
       </c>
     </row>
@@ -1143,32 +1143,32 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>468,000</t>
+          <t>503,000</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>하락 26,000</t>
+          <t>상승 9,000</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-5.26%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>130,221</t>
+          <t>435,128</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>60,871</t>
+          <t>212,094</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>424,628</t>
+          <t>456,385</t>
         </is>
       </c>
     </row>
@@ -1185,32 +1185,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>172,600</t>
+          <t>179,600</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>하락 1,900</t>
+          <t>상승 5,100</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-1.09%</t>
+          <t>+2.92%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>97,747</t>
+          <t>547,892</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>16,768</t>
+          <t>97,614</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>401,388</t>
+          <t>417,666</t>
         </is>
       </c>
     </row>
@@ -1227,32 +1227,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>465,500</t>
+          <t>483,500</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>하락 25,500</t>
+          <t>하락 7,500</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-5.19%</t>
+          <t>-1.53%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>120,577</t>
+          <t>335,398</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>56,338</t>
+          <t>159,940</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>375,126</t>
+          <t>389,631</t>
         </is>
       </c>
     </row>
@@ -1269,32 +1269,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>238,000</t>
+          <t>243,000</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>하락 25,500</t>
+          <t>하락 20,500</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-9.68%</t>
+          <t>-7.78%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>528,418</t>
+          <t>1,140,469</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>127,424</t>
+          <t>277,555</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>357,000</t>
+          <t>364,500</t>
         </is>
       </c>
     </row>
@@ -1311,116 +1311,116 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>942,000</t>
+          <t>988,000</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>하락 70,000</t>
+          <t>하락 24,000</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>-6.92%</t>
+          <t>-2.37%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>45,270</t>
+          <t>203,582</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>43,138</t>
+          <t>203,629</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>339,564</t>
+          <t>356,146</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>042660</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>107,500</t>
+          <t>122,700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>상승 4,200</t>
+          <t>상승 6,300</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>+4.07%</t>
+          <t>+5.41%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1,771,117</t>
+          <t>857,364</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>193,571</t>
+          <t>103,504</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>329,394</t>
+          <t>336,649</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>042660</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>118,200</t>
+          <t>107,500</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>상승 1,800</t>
+          <t>상승 4,200</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>+4.07%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>237,165</t>
+          <t>2,836,980</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>27,556</t>
+          <t>307,792</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>324,303</t>
+          <t>329,394</t>
         </is>
       </c>
     </row>
@@ -1437,116 +1437,116 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3,423,000</t>
+          <t>3,510,000</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>하락 295,000</t>
+          <t>하락 208,000</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>-7.93%</t>
+          <t>-5.59%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>16,664</t>
+          <t>48,566</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>58,460</t>
+          <t>172,401</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>319,179</t>
+          <t>327,292</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>035420</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>193,700</t>
+          <t>197,100</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>하락 3,700</t>
+          <t>상승 3,800</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>+1.97%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>284,455</t>
+          <t>1,665,898</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>54,983</t>
+          <t>319,996</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>303,891</t>
+          <t>321,046</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>035420</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>183,250</t>
+          <t>203,000</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>하락 10,050</t>
+          <t>상승 5,600</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-5.20%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>380,193</t>
+          <t>916,119</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>69,814</t>
+          <t>181,571</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>298,486</t>
+          <t>318,482</t>
         </is>
       </c>
     </row>
@@ -1563,32 +1563,32 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>618,000</t>
+          <t>620,000</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>하락 5,000</t>
+          <t>하락 3,000</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>15,803</t>
+          <t>78,227</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>9,619</t>
+          <t>48,537</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>275,921</t>
+          <t>276,814</t>
         </is>
       </c>
     </row>
@@ -1605,32 +1605,32 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>352,500</t>
+          <t>367,000</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>하락 6,000</t>
+          <t>상승 8,500</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>-1.67%</t>
+          <t>+2.37%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>42,013</t>
+          <t>124,819</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>14,886</t>
+          <t>45,118</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>249,475</t>
+          <t>259,737</t>
         </is>
       </c>
     </row>
@@ -1647,32 +1647,32 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>305,000</t>
+          <t>323,500</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>하락 10,000</t>
+          <t>상승 8,500</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-3.17%</t>
+          <t>+2.70%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69,059</t>
+          <t>250,121</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>21,061</t>
+          <t>78,634</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>241,687</t>
+          <t>256,346</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>37,050</t>
+          <t>38,650</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>하락 550</t>
+          <t>상승 1,050</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>+2.79%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>406,197</t>
+          <t>1,904,681</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>15,015</t>
+          <t>72,833</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>237,848</t>
+          <t>248,119</t>
         </is>
       </c>
     </row>
@@ -1731,116 +1731,116 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1,410,000</t>
+          <t>1,482,000</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>하락 180,000</t>
+          <t>하락 108,000</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>-11.32%</t>
+          <t>-6.79%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>18,525</t>
+          <t>54,065</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>27,085</t>
+          <t>79,791</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>228,333</t>
+          <t>239,993</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>고려아연</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>006800</t>
+          <t>010130</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>39,950</t>
+          <t>1,093,000</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>하락 3,700</t>
+          <t>하락 2,000</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>-8.48%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>628,018</t>
+          <t>12,508</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>25,369</t>
+          <t>13,554</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>223,547</t>
+          <t>228,142</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>고려아연</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>010130</t>
+          <t>006800</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1,066,000</t>
+          <t>40,750</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>하락 29,000</t>
+          <t>하락 2,900</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>-2.65%</t>
+          <t>-6.64%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2,777</t>
+          <t>1,676,312</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2,955</t>
+          <t>68,160</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>222,506</t>
+          <t>228,024</t>
         </is>
       </c>
     </row>
@@ -1857,158 +1857,158 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>29,375</t>
+          <t>30,750</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>상승 25</t>
+          <t>상승 1,400</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+4.77%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>325,827</t>
+          <t>1,591,477</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>9,488</t>
+          <t>47,961</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>213,876</t>
+          <t>223,888</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>064350</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>218,500</t>
+          <t>200,500</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>하락 28,000</t>
+          <t>상승 10,700</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-11.36%</t>
+          <t>+5.64%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>319,077</t>
+          <t>597,887</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>71,926</t>
+          <t>117,251</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>208,257</t>
+          <t>218,830</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>064350</t>
+          <t>011070</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>187,500</t>
+          <t>897,000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>하락 2,300</t>
+          <t>하락 10,000</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>-1.10%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>226,395</t>
+          <t>195,956</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>43,568</t>
+          <t>172,387</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>204,642</t>
+          <t>212,294</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>011070</t>
+          <t>042700</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>857,000</t>
+          <t>222,500</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>하락 50,000</t>
+          <t>하락 24,000</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-5.51%</t>
+          <t>-9.74%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>71,269</t>
+          <t>1,115,853</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>61,095</t>
+          <t>248,966</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>202,827</t>
+          <t>212,070</t>
         </is>
       </c>
     </row>
@@ -2025,32 +2025,32 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>22,550</t>
+          <t>23,400</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>하락 1,200</t>
+          <t>하락 350</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>-5.05%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1,495,358</t>
+          <t>3,819,914</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>34,218</t>
+          <t>88,309</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>198,440</t>
+          <t>205,920</t>
         </is>
       </c>
     </row>
@@ -2067,32 +2067,32 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>275,500</t>
+          <t>285,500</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>하락 4,500</t>
+          <t>상승 5,500</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+1.96%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>43,156</t>
+          <t>127,231</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>11,746</t>
+          <t>35,583</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>194,482</t>
+          <t>201,541</t>
         </is>
       </c>
     </row>
@@ -2109,116 +2109,116 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>85,700</t>
+          <t>88,000</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>하락 2,900</t>
+          <t>하락 600</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>-3.27%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>160,759</t>
+          <t>596,168</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>13,790</t>
+          <t>51,825</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>184,075</t>
+          <t>189,015</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>011200</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>105,800</t>
+          <t>19,500</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>하락 1,100</t>
+          <t>상승 840</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+4.50%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>50,156</t>
+          <t>1,093,927</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>5,322</t>
+          <t>20,956</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>177,053</t>
+          <t>183,931</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>011200</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>18,660</t>
+          <t>108,300</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>보합 0</t>
+          <t>상승 1,400</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>237,144</t>
+          <t>238,131</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4,394</t>
+          <t>25,570</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>176,008</t>
+          <t>181,237</t>
         </is>
       </c>
     </row>
@@ -2235,32 +2235,32 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>168,600</t>
+          <t>174,400</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>상승 1,500</t>
+          <t>상승 7,300</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>+0.90%</t>
+          <t>+4.37%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>29,462</t>
+          <t>187,984</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>4,939</t>
+          <t>32,471</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>175,024</t>
+          <t>181,045</t>
         </is>
       </c>
     </row>
@@ -2277,116 +2277,116 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>742,000</t>
+          <t>771,000</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>하락 28,000</t>
+          <t>상승 1,000</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>-3.64%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>30,773</t>
+          <t>105,083</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>23,509</t>
+          <t>80,416</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>163,240</t>
+          <t>169,620</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>기업은행</t>
+          <t>HD현대</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>024110</t>
+          <t>267250</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>20,250</t>
+          <t>211,500</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>보합 0</t>
+          <t>상승 1,500</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>232,633</t>
+          <t>124,426</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>4,671</t>
+          <t>25,975</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>161,479</t>
+          <t>167,070</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>기업은행</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>024110</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>206,000</t>
+          <t>20,950</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>상승 8,600</t>
+          <t>상승 700</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>+4.36%</t>
+          <t>+3.46%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>285,157</t>
+          <t>928,070</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>58,953</t>
+          <t>19,145</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>159,398</t>
+          <t>167,061</t>
         </is>
       </c>
     </row>
@@ -2403,158 +2403,158 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>93,600</t>
+          <t>96,100</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>하락 4,400</t>
+          <t>하락 1,900</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>-4.49%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>74,330</t>
+          <t>301,307</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>6,974</t>
+          <t>28,618</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>158,233</t>
+          <t>162,460</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>HD현대</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>267250</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>198,300</t>
+          <t>208,000</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>하락 11,700</t>
+          <t>상승 10,600</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>-5.57%</t>
+          <t>+5.37%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>29,940</t>
+          <t>579,582</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>6,012</t>
+          <t>120,320</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>156,643</t>
+          <t>160,946</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>278470</t>
+          <t>035720</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>407,000</t>
+          <t>36,150</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>하락 1,000</t>
+          <t>상승 1,350</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>+3.88%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>135,309</t>
+          <t>1,760,066</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>56,068</t>
+          <t>62,193</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>152,373</t>
+          <t>160,132</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>278470</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>34,250</t>
+          <t>412,000</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>하락 550</t>
+          <t>상승 4,000</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>-1.58%</t>
+          <t>+0.98%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>453,987</t>
+          <t>418,862</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>15,475</t>
+          <t>175,985</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>151,716</t>
+          <t>154,245</t>
         </is>
       </c>
     </row>
@@ -2571,284 +2571,284 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>153,700</t>
+          <t>158,500</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>하락 500</t>
+          <t>상승 4,300</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+2.79%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>92,944</t>
+          <t>368,798</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>14,351</t>
+          <t>57,924</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>149,819</t>
+          <t>154,498</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>포스코퓨처엠</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>003670</t>
+          <t>003550</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>161,400</t>
+          <t>101,000</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>하락 8,800</t>
+          <t>상승 4,400</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>-5.17%</t>
+          <t>+4.55%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>66,373</t>
+          <t>348,236</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>10,741</t>
+          <t>34,117</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>143,559</t>
+          <t>152,704</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>현대글로비스</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>003550</t>
+          <t>086280</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>94,300</t>
+          <t>199,000</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>하락 2,300</t>
+          <t>상승 1,300</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>80,457</t>
+          <t>163,650</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>7,560</t>
+          <t>32,020</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>142,574</t>
+          <t>149,250</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>현대글로비스</t>
+          <t>포스코퓨처엠</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>086280</t>
+          <t>003670</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>188,400</t>
+          <t>165,600</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>하락 9,300</t>
+          <t>하락 4,600</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>-4.70%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>36,168</t>
+          <t>237,786</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>6,899</t>
+          <t>38,974</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>141,300</t>
+          <t>147,295</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>현대오토에버</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>307950</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>72,800</t>
+          <t>523,000</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>하락 4,200</t>
+          <t>하락 1,000</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>-5.45%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>231,129</t>
+          <t>68,878</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>17,269</t>
+          <t>35,156</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>137,533</t>
+          <t>143,427</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>030200</t>
+          <t>272210</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>53,400</t>
+          <t>75,600</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>하락 300</t>
+          <t>하락 1,400</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>46,368</t>
+          <t>480,448</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2,464</t>
+          <t>36,045</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>134,580</t>
+          <t>142,823</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>현대오토에버</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>307950</t>
+          <t>030200</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>491,000</t>
+          <t>54,400</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>하락 33,000</t>
+          <t>상승 700</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>-6.30%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>18,589</t>
+          <t>245,477</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>9,204</t>
+          <t>13,234</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>134,652</t>
+          <t>137,100</t>
         </is>
       </c>
     </row>
@@ -2865,32 +2865,32 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>112,700</t>
+          <t>116,900</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>하락 6,300</t>
+          <t>하락 2,100</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>-5.29%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>103,919</t>
+          <t>347,602</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>11,862</t>
+          <t>40,366</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>125,498</t>
+          <t>130,175</t>
         </is>
       </c>
     </row>
@@ -2907,116 +2907,116 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>221,000</t>
+          <t>229,500</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>하락 7,000</t>
+          <t>상승 1,500</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>31,252</t>
+          <t>162,971</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>6,902</t>
+          <t>37,028</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>123,154</t>
+          <t>127,891</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>387,500</t>
+          <t>110,600</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>하락 11,500</t>
+          <t>상승 1,000</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+0.91%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>45,634</t>
+          <t>188,647</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>17,447</t>
+          <t>20,634</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>120,900</t>
+          <t>124,517</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>107,100</t>
+          <t>391,000</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>하락 2,500</t>
+          <t>하락 8,000</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>-2.28%</t>
+          <t>-2.01%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>31,424</t>
+          <t>178,914</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>3,367</t>
+          <t>70,313</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>120,576</t>
+          <t>121,992</t>
         </is>
       </c>
     </row>
@@ -3033,32 +3033,32 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>244,500</t>
+          <t>245,500</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>하락 500</t>
+          <t>상승 500</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>26,963</t>
+          <t>72,889</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>6,499</t>
+          <t>17,798</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>112,807</t>
+          <t>113,268</t>
         </is>
       </c>
     </row>
@@ -3075,74 +3075,74 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>28,300</t>
+          <t>29,150</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>상승 500</t>
+          <t>상승 1,350</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>+1.80%</t>
+          <t>+4.86%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1,193,894</t>
+          <t>5,467,735</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>33,079</t>
+          <t>157,687</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>104,206</t>
+          <t>107,336</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>카카오뱅크</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>005940</t>
+          <t>323410</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>28,600</t>
+          <t>22,050</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>하락 950</t>
+          <t>상승 1,150</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>-3.21%</t>
+          <t>+5.50%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>86,202</t>
+          <t>792,444</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2,467</t>
+          <t>17,208</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>101,914</t>
+          <t>105,205</t>
         </is>
       </c>
     </row>
@@ -3159,74 +3159,74 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>409,000</t>
+          <t>423,000</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>하락 8,000</t>
+          <t>상승 6,000</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>-1.92%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>9,996</t>
+          <t>37,058</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>4,090</t>
+          <t>15,479</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>101,772</t>
+          <t>105,255</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>카카오뱅크</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>323410</t>
+          <t>005940</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>21,200</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>상승 300</t>
+          <t>하락 550</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>140,940</t>
+          <t>380,792</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2,950</t>
+          <t>11,027</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>101,150</t>
+          <t>103,340</t>
         </is>
       </c>
     </row>
@@ -3243,116 +3243,116 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>219,500</t>
+          <t>220,000</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>하락 6,500</t>
+          <t>하락 6,000</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>-2.65%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>16,592</t>
+          <t>72,045</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>3,634</t>
+          <t>15,982</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>98,409</t>
+          <t>98,634</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>016360</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>49,550</t>
+          <t>110,000</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>하락 2,150</t>
+          <t>하락 2,700</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>-4.16%</t>
+          <t>-2.40%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1,114,114</t>
+          <t>272,324</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>54,962</t>
+          <t>29,917</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>97,118</t>
+          <t>98,230</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>016360</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>108,300</t>
+          <t>49,850</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>하락 4,400</t>
+          <t>하락 1,850</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>-3.90%</t>
+          <t>-3.58%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>67,418</t>
+          <t>2,594,271</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>7,264</t>
+          <t>129,404</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>96,712</t>
+          <t>97,706</t>
         </is>
       </c>
     </row>
@@ -3369,284 +3369,284 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>138,900</t>
+          <t>146,300</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>상승 2,800</t>
+          <t>상승 10,200</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>+2.06%</t>
+          <t>+7.49%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>25,260</t>
+          <t>152,955</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3,444</t>
+          <t>21,935</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>90,980</t>
+          <t>95,827</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>삼양식품</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>003230</t>
+          <t>352820</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1,202,000</t>
+          <t>216,500</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>상승 40,000</t>
+          <t>상승 12,500</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>+3.44%</t>
+          <t>+6.13%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>31,332</t>
+          <t>370,525</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>37,671</t>
+          <t>79,562</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>90,547</t>
+          <t>93,316</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>포스코인터내셔널</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>352820</t>
+          <t>047050</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>210,000</t>
+          <t>52,800</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>상승 6,000</t>
+          <t>상승 1,500</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>+2.94%</t>
+          <t>+2.92%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>102,852</t>
+          <t>364,999</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>21,508</t>
+          <t>19,063</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>90,515</t>
+          <t>92,887</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>포스코인터내셔널</t>
+          <t>이수페타시스</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>047050</t>
+          <t>007660</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>50,400</t>
+          <t>122,200</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>하락 900</t>
+          <t>하락 10,700</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-8.05%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>49,093</t>
+          <t>1,143,920</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2,468</t>
+          <t>142,810</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>88,665</t>
+          <t>89,706</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>이수페타시스</t>
+          <t>한진칼</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>007660</t>
+          <t>180640</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>118,200</t>
+          <t>134,100</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>하락 14,700</t>
+          <t>상승 8,900</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>-11.06%</t>
+          <t>+7.11%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>315,780</t>
+          <t>132,386</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>38,506</t>
+          <t>17,394</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>86,770</t>
+          <t>89,528</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>키움증권</t>
+          <t>삼양식품</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>039490</t>
+          <t>003230</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>320,500</t>
+          <t>1,172,000</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>하락 27,000</t>
+          <t>상승 10,000</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>-7.77%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>15,867</t>
+          <t>64,511</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>5,170</t>
+          <t>77,292</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>84,062</t>
+          <t>88,287</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>한진칼</t>
+          <t>키움증권</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>180640</t>
+          <t>039490</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>124,000</t>
+          <t>329,000</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>하락 1,200</t>
+          <t>하락 18,500</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>-5.32%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>15,431</t>
+          <t>68,519</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1,913</t>
+          <t>22,568</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>82,785</t>
+          <t>86,291</t>
         </is>
       </c>
     </row>
@@ -3663,116 +3663,116 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>63,050</t>
+          <t>67,800</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>상승 250</t>
+          <t>상승 5,000</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>+7.96%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>60,868</t>
+          <t>250,740</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>3,841</t>
+          <t>16,447</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>78,103</t>
+          <t>83,987</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>LG씨엔에스</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>064400</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>18,620</t>
+          <t>80,500</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>하락 800</t>
+          <t>상승 4,300</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>-4.12%</t>
+          <t>+5.64%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1,603,471</t>
+          <t>2,405,745</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>29,965</t>
+          <t>190,155</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>76,511</t>
+          <t>77,993</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LG씨엔에스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>064400</t>
+          <t>047040</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>77,100</t>
+          <t>18,810</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>상승 900</t>
+          <t>하락 610</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>+1.18%</t>
+          <t>-3.14%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>816,467</t>
+          <t>3,928,458</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>62,646</t>
+          <t>74,166</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>74,699</t>
+          <t>77,292</t>
         </is>
       </c>
     </row>
@@ -3789,284 +3789,284 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>239,000</t>
+          <t>243,000</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>하락 22,500</t>
+          <t>하락 18,500</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>-8.60%</t>
+          <t>-7.07%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>123,314</t>
+          <t>321,895</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>29,832</t>
+          <t>78,840</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>73,172</t>
+          <t>74,397</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>신세계</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>004170</t>
+          <t>000880</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>735,000</t>
+          <t>105,200</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>하락 41,000</t>
+          <t>상승 3,500</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>-5.28%</t>
+          <t>+3.44%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>13,273</t>
+          <t>185,555</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>9,782</t>
+          <t>18,909</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>69,422</t>
+          <t>74,174</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>090430</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>118,400</t>
+          <t>78,200</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>상승 4,800</t>
+          <t>상승 5,200</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>+4.23%</t>
+          <t>+7.12%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>178,507</t>
+          <t>352,131</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20,950</t>
+          <t>26,775</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>69,255</t>
+          <t>72,644</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>아모레퍼시픽</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>090430</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>73,400</t>
+          <t>121,200</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>상승 400</t>
+          <t>상승 7,600</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>+6.69%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>38,871</t>
+          <t>620,781</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2,805</t>
+          <t>74,687</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>68,185</t>
+          <t>70,893</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>신세계</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>000880</t>
+          <t>004170</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>96,600</t>
+          <t>744,000</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>하락 5,100</t>
+          <t>하락 32,000</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>-5.01%</t>
+          <t>-4.12%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>58,800</t>
+          <t>45,649</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>5,715</t>
+          <t>33,941</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>68,111</t>
+          <t>70,272</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>코웨이</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>021240</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>95,700</t>
+          <t>88,000</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>상승 700</t>
+          <t>상승 1,300</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>+0.74%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>22,757</t>
+          <t>92,854</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2,160</t>
+          <t>8,074</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>67,724</t>
+          <t>68,916</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>코웨이</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>021240</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>85,600</t>
+          <t>97,100</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>하락 1,100</t>
+          <t>상승 2,100</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>-1.27%</t>
+          <t>+2.21%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>18,689</t>
+          <t>154,137</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1,588</t>
+          <t>15,108</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>67,036</t>
+          <t>68,715</t>
         </is>
       </c>
     </row>
@@ -4083,32 +4083,32 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>33,600</t>
+          <t>34,400</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>하락 3,200</t>
+          <t>하락 2,400</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>-8.70%</t>
+          <t>-6.52%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1,358,445</t>
+          <t>2,761,814</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>46,513</t>
+          <t>95,094</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>65,854</t>
+          <t>67,421</t>
         </is>
       </c>
     </row>
@@ -4125,32 +4125,32 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>63,200</t>
+          <t>64,600</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>하락 500</t>
+          <t>상승 900</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>+1.41%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>25,380</t>
+          <t>137,002</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1,601</t>
+          <t>8,857</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>60,581</t>
+          <t>61,923</t>
         </is>
       </c>
     </row>
@@ -4167,158 +4167,158 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>14,020</t>
+          <t>14,440</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>하락 130</t>
+          <t>상승 290</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+2.05%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>99,543</t>
+          <t>682,581</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1,397</t>
+          <t>9,743</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>59,505</t>
+          <t>61,287</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HD건설기계</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>267270</t>
+          <t>009830</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>121,500</t>
+          <t>35,450</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>하락 4,100</t>
+          <t>하락 650</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>-3.26%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>36,824</t>
+          <t>2,556,616</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>4,445</t>
+          <t>90,434</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>58,225</t>
+          <t>60,936</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>HD건설기계</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>267270</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>33,150</t>
+          <t>123,800</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>하락 2,950</t>
+          <t>하락 1,800</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>-8.17%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>794,366</t>
+          <t>160,927</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>27,056</t>
+          <t>19,813</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>56,982</t>
+          <t>59,327</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>오리온</t>
+          <t>한미약품</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>271560</t>
+          <t>128940</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>143,800</t>
+          <t>458,500</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>상승 7,100</t>
+          <t>상승 36,500</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>+5.19%</t>
+          <t>+8.65%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>30,218</t>
+          <t>138,001</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>4,262</t>
+          <t>60,238</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>56,853</t>
+          <t>58,738</t>
         </is>
       </c>
     </row>
@@ -4335,242 +4335,242 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>259,500</t>
+          <t>268,000</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>상승 4,000</t>
+          <t>상승 12,500</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>+4.89%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>19,059</t>
+          <t>97,206</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>4,916</t>
+          <t>25,912</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>55,907</t>
+          <t>57,738</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>000100</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>69,600</t>
+          <t>18,360</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>하락 900</t>
+          <t>상승 1,040</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>+6.00%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>65,369</t>
+          <t>882,794</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>4,519</t>
+          <t>16,001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>55,435</t>
+          <t>56,976</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>삼성카드</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>029780</t>
+          <t>000100</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>47,650</t>
+          <t>71,000</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>상승 450</t>
+          <t>상승 500</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>14,676</t>
+          <t>249,355</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>17,605</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>55,207</t>
+          <t>56,550</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>삼성카드</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>029780</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>17,630</t>
+          <t>48,650</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>상승 310</t>
+          <t>상승 1,450</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>+1.79%</t>
+          <t>+3.07%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>157,944</t>
+          <t>79,989</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2,750</t>
+          <t>3,864</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>54,711</t>
+          <t>56,365</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>오리온</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>271560</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>10,890</t>
+          <t>142,300</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>하락 260</t>
+          <t>상승 5,600</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>+4.10%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>991,141</t>
+          <t>150,307</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>10,709</t>
+          <t>21,560</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>54,450</t>
+          <t>56,260</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>128940</t>
+          <t>034220</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>424,000</t>
+          <t>11,220</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>상승 2,000</t>
+          <t>상승 70</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>20,210</t>
+          <t>3,741,805</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>8,428</t>
+          <t>41,814</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>54,319</t>
+          <t>56,100</t>
         </is>
       </c>
     </row>
@@ -4587,116 +4587,116 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>40,100</t>
+          <t>41,200</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>하락 1,000</t>
+          <t>상승 100</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>-2.43%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>40,291</t>
+          <t>152,482</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1,608</t>
+          <t>6,240</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>54,240</t>
+          <t>55,728</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DB하이텍</t>
+          <t>두산로보틱스</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>000990</t>
+          <t>454910</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>124,500</t>
+          <t>85,300</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>하락 8,700</t>
+          <t>하락 4,000</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>-6.53%</t>
+          <t>-4.48%</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>160,523</t>
+          <t>551,111</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>19,980</t>
+          <t>46,352</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>54,163</t>
+          <t>55,291</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>두산로보틱스</t>
+          <t>DB하이텍</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>454910</t>
+          <t>000990</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>82,100</t>
+          <t>118,700</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>하락 7,200</t>
+          <t>하락 14,500</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>-8.06%</t>
+          <t>-10.89%</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>241,573</t>
+          <t>1,080,614</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20,028</t>
+          <t>131,697</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>53,217</t>
+          <t>51,640</t>
         </is>
       </c>
     </row>
@@ -4713,158 +4713,158 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>98,800</t>
+          <t>100,600</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>하락 5,900</t>
+          <t>하락 4,100</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>-5.64%</t>
+          <t>-3.92%</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>102,337</t>
+          <t>220,848</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>10,100</t>
+          <t>22,022</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>49,003</t>
+          <t>49,896</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>JB금융지주</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>175330</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>171,000</t>
+          <t>25,750</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>하락 14,000</t>
+          <t>상승 1,250</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>-7.57%</t>
+          <t>+5.10%</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>34,355</t>
+          <t>288,471</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>5,886</t>
+          <t>7,331</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>48,374</t>
+          <t>48,475</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CJ</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>001040</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>159,500</t>
+          <t>170,200</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>하락 500</t>
+          <t>하락 14,800</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-8.00%</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>16,056</t>
+          <t>170,254</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2,554</t>
+          <t>28,795</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>46,537</t>
+          <t>48,147</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>JB금융지주</t>
+          <t>CJ</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>175330</t>
+          <t>001040</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>24,550</t>
+          <t>162,100</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>상승 50</t>
+          <t>상승 2,100</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>32,756</t>
+          <t>84,086</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>13,769</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>46,216</t>
+          <t>47,296</t>
         </is>
       </c>
     </row>
@@ -4881,32 +4881,32 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>52,300</t>
+          <t>54,100</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>하락 2,700</t>
+          <t>하락 900</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>443,588</t>
+          <t>955,168</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>24,272</t>
+          <t>51,440</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>43,643</t>
+          <t>45,145</t>
         </is>
       </c>
     </row>
@@ -4923,200 +4923,200 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>106,600</t>
+          <t>107,700</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>하락 3,400</t>
+          <t>하락 2,300</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>79,990</t>
+          <t>230,918</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>8,575</t>
+          <t>24,815</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>43,245</t>
+          <t>43,692</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>OCI홀딩스</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>010060</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>227,000</t>
+          <t>109,800</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>하락 13,000</t>
+          <t>하락 4,100</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>-5.42%</t>
+          <t>-3.60%</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>83,304</t>
+          <t>77,006</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>19,558</t>
+          <t>8,445</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>42,381</t>
+          <t>41,966</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>OCI홀딩스</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>010060</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>108,000</t>
+          <t>222,500</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>하락 5,900</t>
+          <t>하락 17,500</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>-5.18%</t>
+          <t>-7.29%</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>27,534</t>
+          <t>216,761</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>3,014</t>
+          <t>50,164</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>41,278</t>
+          <t>41,541</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>현대백화점</t>
+          <t>KCC</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>069960</t>
+          <t>002380</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>188,500</t>
+          <t>478,500</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>하락 5,500</t>
+          <t>상승 1,500</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>20,784</t>
+          <t>27,172</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>3,907</t>
+          <t>12,770</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>40,650</t>
+          <t>41,117</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>KCC</t>
+          <t>현대백화점</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>002380</t>
+          <t>069960</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>457,000</t>
+          <t>189,700</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>하락 20,000</t>
+          <t>하락 4,300</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>-4.19%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>6,354</t>
+          <t>92,959</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2,871</t>
+          <t>17,621</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>39,270</t>
+          <t>40,909</t>
         </is>
       </c>
     </row>
@@ -5133,32 +5133,32 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>3,670</t>
+          <t>3,820</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>하락 115</t>
+          <t>상승 35</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>-3.04%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>1,521,180</t>
+          <t>5,269,092</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>5,553</t>
+          <t>19,867</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>37,664</t>
+          <t>39,203</t>
         </is>
       </c>
     </row>
@@ -5175,32 +5175,32 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>4,330</t>
+          <t>4,465</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>하락 50</t>
+          <t>상승 85</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>+1.94%</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>927,272</t>
+          <t>2,280,143</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>3,933</t>
+          <t>9,948</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>37,607</t>
+          <t>38,780</t>
         </is>
       </c>
     </row>
@@ -5217,32 +5217,32 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>27,750</t>
+          <t>28,550</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>하락 600</t>
+          <t>상승 200</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>-2.12%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>109,597</t>
+          <t>408,249</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>3,010</t>
+          <t>11,523</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>37,031</t>
+          <t>38,099</t>
         </is>
       </c>
     </row>
@@ -5259,32 +5259,32 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>82,400</t>
+          <t>83,200</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>상승 8,200</t>
+          <t>상승 9,000</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>+11.05%</t>
+          <t>+12.13%</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>24,586</t>
+          <t>183,827</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>1,938</t>
+          <t>15,425</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>36,513</t>
+          <t>36,867</t>
         </is>
       </c>
     </row>
@@ -5301,32 +5301,32 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>238,500</t>
+          <t>246,000</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>상승 2,500</t>
+          <t>상승 10,000</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>+1.06%</t>
+          <t>+4.24%</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>14,251</t>
+          <t>71,632</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>3,352</t>
+          <t>17,396</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>35,717</t>
+          <t>36,840</t>
         </is>
       </c>
     </row>
@@ -5343,32 +5343,32 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>22,200</t>
+          <t>22,650</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>하락 500</t>
+          <t>하락 50</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>-2.20%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>138,539</t>
+          <t>414,756</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>3,068</t>
+          <t>9,334</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>33,752</t>
+          <t>34,436</t>
         </is>
       </c>
     </row>
@@ -5385,32 +5385,32 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>63,800</t>
+          <t>62,600</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>상승 2,200</t>
+          <t>상승 1,000</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>+3.57%</t>
+          <t>+1.62%</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>196,213</t>
+          <t>507,171</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>12,271</t>
+          <t>32,071</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>33,330</t>
+          <t>32,703</t>
         </is>
       </c>
     </row>
@@ -5427,32 +5427,32 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>14,390</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>상승 90</t>
+          <t>상승 600</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>+4.20%</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>76,138</t>
+          <t>441,262</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>1,090</t>
+          <t>6,496</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>30,786</t>
+          <t>31,877</t>
         </is>
       </c>
     </row>
@@ -5469,452 +5469,452 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>37,650</t>
+          <t>38,800</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>하락 150</t>
+          <t>상승 1,000</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>-0.40%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>14,615</t>
+          <t>89,550</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>3,451</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>30,848</t>
+          <t>31,791</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>243,500</t>
+          <t>36,250</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>상승 2,000</t>
+          <t>상승 1,850</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>+0.83%</t>
+          <t>+5.38%</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>78,464</t>
+          <t>431,940</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>19,565</t>
+          <t>15,588</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>30,400</t>
+          <t>30,902</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>한솔케미칼</t>
+          <t>F&amp;F</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>014680</t>
+          <t>383220</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>275,500</t>
+          <t>80,300</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>하락 28,500</t>
+          <t>상승 2,900</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>-9.37%</t>
+          <t>+3.75%</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>8,620</t>
+          <t>83,968</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2,455</t>
+          <t>6,797</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>30,341</t>
+          <t>30,761</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>F&amp;F</t>
+          <t>한솔케미칼</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>383220</t>
+          <t>014680</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>79,300</t>
+          <t>280,000</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>상승 1,900</t>
+          <t>하락 24,000</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>-7.89%</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>8,837</t>
+          <t>27,666</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>7,852</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>30,378</t>
+          <t>30,836</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>한국가스공사</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>036460</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>35,450</t>
+          <t>33,150</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>상승 1,050</t>
+          <t>상승 600</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>+3.05%</t>
+          <t>+1.84%</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>77,336</t>
+          <t>109,225</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2,687</t>
+          <t>3,598</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>30,220</t>
+          <t>30,602</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>한국가스공사</t>
+          <t>CJ제일제당</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>036460</t>
+          <t>097950</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>32,600</t>
+          <t>198,000</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>상승 50</t>
+          <t>상승 10,200</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+5.43%</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>31,495</t>
+          <t>90,216</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>1,015</t>
+          <t>17,776</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>30,094</t>
+          <t>29,807</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CJ제일제당</t>
+          <t>금호석유화학</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>097950</t>
+          <t>011780</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>195,400</t>
+          <t>118,400</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>상승 7,600</t>
+          <t>상승 2,000</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>+4.05%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>23,635</t>
+          <t>69,728</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>4,550</t>
+          <t>8,161</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>29,416</t>
+          <t>29,786</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>금호석유화학</t>
+          <t>SK바이오사이언스</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>011780</t>
+          <t>302440</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>113,000</t>
+          <t>37,900</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>하락 3,400</t>
+          <t>상승 1,200</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>-2.92%</t>
+          <t>+3.27%</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>9,705</t>
+          <t>87,482</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>1,096</t>
+          <t>3,264</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>28,428</t>
+          <t>29,735</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SK바이오사이언스</t>
+          <t>에코프로머티</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>302440</t>
+          <t>450080</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>35,950</t>
+          <t>40,700</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>하락 750</t>
+          <t>하락 1,200</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>-2.86%</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>15,677</t>
+          <t>423,694</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>17,036</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>28,205</t>
+          <t>28,777</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>현대엘리베이터</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>017800</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>71,900</t>
+          <t>226,000</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>하락 600</t>
+          <t>하락 15,500</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>-0.83%</t>
+          <t>-6.42%</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>18,996</t>
+          <t>250,115</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>1,359</t>
+          <t>60,844</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>28,107</t>
+          <t>28,215</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>에코프로머티</t>
+          <t>현대엘리베이터</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>450080</t>
+          <t>017800</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>39,400</t>
+          <t>72,200</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>하락 2,500</t>
+          <t>하락 300</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>-5.97%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>166,867</t>
+          <t>87,947</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>6,604</t>
+          <t>6,389</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>27,858</t>
+          <t>28,225</t>
         </is>
       </c>
     </row>
@@ -5931,368 +5931,368 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>72,800</t>
+          <t>73,900</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>상승 400</t>
+          <t>상승 1,500</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>+2.07%</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>6,438</t>
+          <t>49,769</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>3,689</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>27,663</t>
+          <t>28,081</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>iM금융지주</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>139130</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>116,700</t>
+          <t>17,410</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>상승 9,900</t>
+          <t>상승 530</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>+9.27%</t>
+          <t>+3.14%</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>301,966</t>
+          <t>426,761</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>34,910</t>
+          <t>7,402</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>27,547</t>
+          <t>27,965</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>iM금융지주</t>
+          <t>롯데케미칼</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>139130</t>
+          <t>011170</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>16,920</t>
+          <t>65,100</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>상승 40</t>
+          <t>상승 700</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>54,544</t>
+          <t>80,275</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>5,153</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>27,178</t>
+          <t>27,847</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>롯데케미칼</t>
+          <t>에스엘</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>011170</t>
+          <t>005850</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>62,500</t>
+          <t>58,200</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>하락 1,900</t>
+          <t>하락 200</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>15,573</t>
+          <t>62,199</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>3,576</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>26,735</t>
+          <t>27,033</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>161890</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>4,850</t>
+          <t>113,600</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>상승 50</t>
+          <t>상승 6,800</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>+6.37%</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>489,137</t>
+          <t>1,095,322</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2,359</t>
+          <t>129,035</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>25,927</t>
+          <t>26,815</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>에스엘</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>005850</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>55,100</t>
+          <t>5,020</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>하락 3,300</t>
+          <t>상승 220</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>-5.65%</t>
+          <t>+4.58%</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>13,810</t>
+          <t>1,916,085</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>9,454</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>25,593</t>
+          <t>26,835</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>동서</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>026960</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>64,500</t>
+          <t>25,850</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>하락 2,300</t>
+          <t>상승 1,900</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>-3.44%</t>
+          <t>+7.93%</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>118,955</t>
+          <t>237,267</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>7,665</t>
+          <t>6,054</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>24,957</t>
+          <t>25,772</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>미스토홀딩스</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>081660</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>46,500</t>
+          <t>65,200</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>상승 3,400</t>
+          <t>하락 1,600</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>+7.89%</t>
+          <t>-2.40%</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>53,699</t>
+          <t>373,207</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2,446</t>
+          <t>24,280</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>24,688</t>
+          <t>25,228</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>동서</t>
+          <t>미스토홀딩스</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>026960</t>
+          <t>081660</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>24,700</t>
+          <t>46,950</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>상승 750</t>
+          <t>상승 3,850</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>+3.13%</t>
+          <t>+8.93%</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>29,951</t>
+          <t>276,502</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>13,082</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>24,626</t>
+          <t>24,927</t>
         </is>
       </c>
     </row>
@@ -6309,116 +6309,116 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>23,450</t>
+          <t>24,550</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>하락 300</t>
+          <t>상승 800</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>-1.26%</t>
+          <t>+3.37%</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>24,059</t>
+          <t>123,957</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>2,991</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>23,371</t>
+          <t>24,467</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>영원무역홀딩스</t>
+          <t>한국앤컴퍼니</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>009970</t>
+          <t>000240</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>180,000</t>
+          <t>25,200</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>상승 11,800</t>
+          <t>상승 1,000</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>+7.02%</t>
+          <t>+4.13%</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>3,267</t>
+          <t>76,832</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>1,918</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>23,317</t>
+          <t>23,924</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>한국앤컴퍼니</t>
+          <t>영원무역홀딩스</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>000240</t>
+          <t>009970</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>24,350</t>
+          <t>181,700</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>상승 150</t>
+          <t>상승 13,500</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>+8.03%</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>10,269</t>
+          <t>19,351</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>3,537</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>23,117</t>
+          <t>23,537</t>
         </is>
       </c>
     </row>
@@ -6435,410 +6435,410 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>83,000</t>
+          <t>84,300</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>상승 600</t>
+          <t>상승 1,900</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>+0.73%</t>
+          <t>+2.31%</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>20,933</t>
+          <t>85,487</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>1,719</t>
+          <t>7,162</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>22,905</t>
+          <t>23,263</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>HD현대마린엔진</t>
+          <t>HL만도</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>071970</t>
+          <t>204320</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>65,600</t>
+          <t>49,350</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>하락 3,200</t>
+          <t>상승 1,250</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>-4.65%</t>
+          <t>+2.60%</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>66,836</t>
+          <t>1,075,846</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>4,452</t>
+          <t>52,707</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>22,252</t>
+          <t>23,173</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>HL만도</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>204320</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>46,650</t>
+          <t>38,150</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>하락 1,450</t>
+          <t>상승 50</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>-3.01%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>192,129</t>
+          <t>78,991</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>8,950</t>
+          <t>2,967</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>21,905</t>
+          <t>22,322</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>농심</t>
+          <t>HD현대마린엔진</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>004370</t>
+          <t>071970</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>354,000</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>상승 13,000</t>
+          <t>하락 3,800</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>+3.81%</t>
+          <t>-5.52%</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>10,244</t>
+          <t>194,024</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>3,587</t>
+          <t>12,785</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>21,533</t>
+          <t>22,049</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>농심</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>004370</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>36,600</t>
+          <t>362,000</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>하락 1,500</t>
+          <t>상승 21,000</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>-3.94%</t>
+          <t>+6.16%</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>16,218</t>
+          <t>41,533</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>14,977</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>21,415</t>
+          <t>22,019</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>제일기획</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>030000</t>
+          <t>008930</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>18,480</t>
+          <t>32,100</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>상승 200</t>
+          <t>상승 1,450</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+4.73%</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>96,744</t>
+          <t>89,128</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>1,774</t>
+          <t>2,781</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>21,260</t>
+          <t>21,954</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>제일기획</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>030000</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>30,550</t>
+          <t>18,710</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>하락 100</t>
+          <t>상승 430</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+2.35%</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>12,451</t>
+          <t>448,362</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>8,366</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>20,894</t>
+          <t>21,524</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>이수스페셜티케미컬</t>
+          <t>GS리테일</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>457190</t>
+          <t>007070</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>67,800</t>
+          <t>25,200</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>하락 3,700</t>
+          <t>상승 1,600</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>-5.17%</t>
+          <t>+6.78%</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>28,887</t>
+          <t>240,643</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>1,967</t>
+          <t>6,019</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>20,488</t>
+          <t>21,069</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>GS리테일</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>007070</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>24,500</t>
+          <t>121,200</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>상승 900</t>
+          <t>상승 5,600</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>+3.81%</t>
+          <t>+4.84%</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>34,308</t>
+          <t>60,552</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>7,306</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>20,484</t>
+          <t>20,948</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>이수스페셜티케미컬</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>457190</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>118,400</t>
+          <t>68,100</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>상승 2,800</t>
+          <t>하락 3,400</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>+2.42%</t>
+          <t>-4.76%</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>7,451</t>
+          <t>81,469</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>5,574</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>20,464</t>
+          <t>20,579</t>
         </is>
       </c>
     </row>
@@ -6855,200 +6855,200 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>45,050</t>
+          <t>45,550</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>하락 900</t>
+          <t>하락 400</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>28,293</t>
+          <t>75,601</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>1,277</t>
+          <t>3,447</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>20,272</t>
+          <t>20,498</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>호텔신라</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>008770</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>175,000</t>
+          <t>50,700</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>상승 9,700</t>
+          <t>상승 3,600</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>+5.87%</t>
+          <t>+7.64%</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>40,838</t>
+          <t>524,653</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>7,078</t>
+          <t>26,949</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>19,862</t>
+          <t>19,899</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>호텔신라</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>008770</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>47,250</t>
+          <t>170,100</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>상승 150</t>
+          <t>상승 4,800</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+2.90%</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>32,805</t>
+          <t>107,362</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>1,529</t>
+          <t>18,736</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>18,545</t>
+          <t>19,306</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>아모레퍼시픽홀딩스</t>
+          <t>씨에스윈드</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>002790</t>
+          <t>112610</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>23,950</t>
+          <t>44,800</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>상승 900</t>
+          <t>하락 600</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>+3.90%</t>
+          <t>-1.32%</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>52,933</t>
+          <t>547,420</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>1,251</t>
+          <t>24,433</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>18,312</t>
+          <t>18,893</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>씨에스윈드</t>
+          <t>아모레퍼시픽홀딩스</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>112610</t>
+          <t>002790</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>43,200</t>
+          <t>24,500</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>하락 2,200</t>
+          <t>상승 1,450</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>-4.85%</t>
+          <t>+6.29%</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>163,231</t>
+          <t>266,673</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>7,102</t>
+          <t>6,555</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>18,218</t>
+          <t>18,732</t>
         </is>
       </c>
     </row>
@@ -7065,32 +7065,32 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>64,500</t>
+          <t>66,200</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>하락 1,600</t>
+          <t>상승 100</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>24,190</t>
+          <t>76,477</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>1,558</t>
+          <t>5,012</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>18,076</t>
+          <t>18,552</t>
         </is>
       </c>
     </row>
@@ -7107,74 +7107,74 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>59,800</t>
+          <t>60,900</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>하락 2,300</t>
+          <t>하락 1,200</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>-3.70%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>14,712</t>
+          <t>119,198</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>7,236</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>17,908</t>
+          <t>18,237</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>현대위아</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>011210</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>16,060</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>하락 1,250</t>
+          <t>상승 500</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>-7.22%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>1,764,217</t>
+          <t>96,896</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>28,698</t>
+          <t>6,173</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>17,225</t>
+          <t>17,677</t>
         </is>
       </c>
     </row>
@@ -7191,74 +7191,74 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>75,300</t>
+          <t>76,700</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>보합 0</t>
+          <t>상승 1,400</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>10,128</t>
+          <t>54,689</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>4,184</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>17,178</t>
+          <t>17,497</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>현대위아</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>011210</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>61,900</t>
+          <t>15,520</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>하락 2,600</t>
+          <t>하락 1,790</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>-4.03%</t>
+          <t>-10.34%</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>30,732</t>
+          <t>4,207,710</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>1,902</t>
+          <t>67,072</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>16,834</t>
+          <t>16,646</t>
         </is>
       </c>
     </row>
@@ -7275,32 +7275,32 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>25,600</t>
+          <t>25,950</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>상승 400</t>
+          <t>상승 750</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>+1.59%</t>
+          <t>+2.98%</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>18,150</t>
+          <t>69,189</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>1,793</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>16,037</t>
+          <t>16,256</t>
         </is>
       </c>
     </row>
@@ -7317,32 +7317,32 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>33,100</t>
+          <t>33,950</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>상승 50</t>
+          <t>상승 900</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+2.72%</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>12,116</t>
+          <t>65,330</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>2,194</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>14,611</t>
+          <t>14,986</t>
         </is>
       </c>
     </row>
@@ -7359,32 +7359,32 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>125,100</t>
+          <t>125,400</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>상승 6,800</t>
+          <t>상승 7,100</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>+5.75%</t>
+          <t>+6.00%</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>10,371</t>
+          <t>36,075</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>1,262</t>
+          <t>4,528</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>14,495</t>
+          <t>14,530</t>
         </is>
       </c>
     </row>
@@ -7401,32 +7401,32 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>122,400</t>
+          <t>123,700</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>하락 1,600</t>
+          <t>하락 300</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>7,516</t>
+          <t>21,366</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>2,630</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>14,304</t>
+          <t>14,456</t>
         </is>
       </c>
     </row>
@@ -7443,32 +7443,32 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>65,200</t>
+          <t>66,000</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>상승 200</t>
+          <t>상승 1,000</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>4,997</t>
+          <t>61,964</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>4,113</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>13,805</t>
+          <t>13,974</t>
         </is>
       </c>
     </row>
@@ -7485,116 +7485,116 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>26,500</t>
+          <t>26,800</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>하락 1,000</t>
+          <t>하락 700</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>-3.64%</t>
+          <t>-2.55%</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>56,520</t>
+          <t>147,459</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>1,515</t>
+          <t>3,967</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>13,694</t>
+          <t>13,849</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>파라다이스</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>034230</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>4,765</t>
+          <t>14,860</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>하락 295</t>
+          <t>상승 420</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>-5.83%</t>
+          <t>+2.91%</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>1,089,957</t>
+          <t>680,600</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>5,180</t>
+          <t>10,179</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>13,688</t>
+          <t>13,765</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>파라다이스</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>034230</t>
+          <t>073240</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>14,610</t>
+          <t>4,775</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>상승 170</t>
+          <t>하락 285</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>+1.18%</t>
+          <t>-5.63%</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>87,518</t>
+          <t>2,326,226</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>1,271</t>
+          <t>11,135</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>13,533</t>
+          <t>13,717</t>
         </is>
       </c>
     </row>
@@ -7611,32 +7611,32 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>15,820</t>
+          <t>16,190</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>하락 540</t>
+          <t>하락 170</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>-3.30%</t>
+          <t>-1.04%</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>26,384</t>
+          <t>83,547</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>1,342</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>12,939</t>
+          <t>13,241</t>
         </is>
       </c>
     </row>
@@ -7653,32 +7653,32 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>313,000</t>
+          <t>321,000</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>상승 4,500</t>
+          <t>상승 12,500</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+4.05%</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>4,408</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>1,408</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>12,544</t>
+          <t>12,865</t>
         </is>
       </c>
     </row>
@@ -7695,32 +7695,32 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>282,000</t>
+          <t>283,500</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>하락 8,500</t>
+          <t>하락 7,000</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>3,106</t>
+          <t>14,094</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>4,028</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>12,204</t>
+          <t>12,269</t>
         </is>
       </c>
     </row>
@@ -7737,32 +7737,32 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>44,850</t>
+          <t>45,800</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>하락 500</t>
+          <t>상승 450</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>-1.10%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>7,377</t>
+          <t>34,855</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>1,586</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>11,571</t>
+          <t>11,816</t>
         </is>
       </c>
     </row>
@@ -7779,32 +7779,32 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>32,200</t>
+          <t>32,350</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>하락 2,250</t>
+          <t>하락 2,100</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>-6.53%</t>
+          <t>-6.10%</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>22,734</t>
+          <t>97,239</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>3,164</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>11,548</t>
+          <t>11,601</t>
         </is>
       </c>
     </row>
@@ -7821,32 +7821,32 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>14,920</t>
+          <t>15,150</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>상승 370</t>
+          <t>상승 600</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>+2.54%</t>
+          <t>+4.12%</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>43,723</t>
+          <t>179,376</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>2,698</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>10,464</t>
+          <t>10,625</t>
         </is>
       </c>
     </row>
@@ -7863,32 +7863,32 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>14,130</t>
+          <t>14,120</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>하락 80</t>
+          <t>하락 90</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.63%</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>18,416</t>
+          <t>93,595</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>1,323</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>10,392</t>
+          <t>10,385</t>
         </is>
       </c>
     </row>
@@ -7905,74 +7905,74 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>17,410</t>
+          <t>17,780</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>상승 30</t>
+          <t>상승 400</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>10,686</t>
+          <t>57,115</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>1,009</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>10,123</t>
+          <t>10,338</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>롯데칠성</t>
+          <t>DL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>005300</t>
+          <t>000210</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>102,300</t>
+          <t>46,450</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>상승 3,700</t>
+          <t>상승 900</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>+3.75%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>5,404</t>
+          <t>76,612</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>3,519</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>9,492</t>
+          <t>9,734</t>
         </is>
       </c>
     </row>
@@ -7989,116 +7989,116 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>840,000</t>
+          <t>870,000</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>하락 5,000</t>
+          <t>상승 25,000</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>+2.96%</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>1,994</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>1,711</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>9,353</t>
+          <t>9,687</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>DL</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>000210</t>
+          <t>185750</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>44,250</t>
+          <t>68,600</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>하락 1,300</t>
+          <t>상승 900</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>+1.33%</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>12,559</t>
+          <t>23,757</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>1,614</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>9,273</t>
+          <t>9,469</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>롯데칠성</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>185750</t>
+          <t>005300</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>66,900</t>
+          <t>101,700</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>하락 800</t>
+          <t>상승 3,100</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+3.14%</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>4,647</t>
+          <t>21,228</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>2,180</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>9,234</t>
+          <t>9,437</t>
         </is>
       </c>
     </row>
@@ -8115,32 +8115,32 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>99,600</t>
+          <t>102,300</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>상승 3,500</t>
+          <t>상승 6,200</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>+3.64%</t>
+          <t>+6.45%</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2,671</t>
+          <t>16,589</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>1,681</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>9,168</t>
+          <t>9,416</t>
         </is>
       </c>
     </row>
@@ -8157,32 +8157,32 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>92,200</t>
+          <t>93,900</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>하락 7,900</t>
+          <t>하락 6,200</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>-7.89%</t>
+          <t>-6.19%</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>16,665</t>
+          <t>57,429</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>1,588</t>
+          <t>5,427</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>8,254</t>
+          <t>8,406</t>
         </is>
       </c>
     </row>
@@ -8199,32 +8199,32 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>33,300</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>상승 200</t>
+          <t>상승 900</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>+0.60%</t>
+          <t>+2.72%</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>5,877</t>
+          <t>41,596</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>1,405</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>7,837</t>
+          <t>8,002</t>
         </is>
       </c>
     </row>
@@ -8241,32 +8241,32 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>6,400</t>
+          <t>6,590</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>하락 10</t>
+          <t>상승 180</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+2.81%</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>15,992</t>
+          <t>62,326</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>404</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>7,728</t>
+          <t>7,957</t>
         </is>
       </c>
     </row>
@@ -8283,200 +8283,200 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>65,400</t>
+          <t>66,800</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>보합 0</t>
+          <t>상승 1,400</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>1,944</t>
+          <t>10,434</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>696</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>7,572</t>
+          <t>7,735</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>영풍</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>000670</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>39,200</t>
+          <t>112,700</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>하락 1,200</t>
+          <t>하락 700</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>-2.97%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2,391</t>
+          <t>8,658</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>968</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>7,217</t>
+          <t>7,326</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>HS효성첨단소재</t>
+          <t>영풍</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>298050</t>
+          <t>000670</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>159,500</t>
+          <t>39,600</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>하락 5,300</t>
+          <t>하락 800</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>-3.22%</t>
+          <t>-1.98%</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2,289</t>
+          <t>9,148</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>363</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>7,146</t>
+          <t>7,291</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>SK케미칼</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>285130</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>109,400</t>
+          <t>41,950</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>하락 4,000</t>
+          <t>상승 1,000</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>-3.53%</t>
+          <t>+2.44%</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2,365</t>
+          <t>45,583</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>1,891</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>7,111</t>
+          <t>7,257</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SK케미칼</t>
+          <t>HS효성첨단소재</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>285130</t>
+          <t>298050</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>40,900</t>
+          <t>161,000</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>하락 50</t>
+          <t>하락 3,800</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-2.31%</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>11,557</t>
+          <t>10,172</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>1,641</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>7,075</t>
+          <t>7,213</t>
         </is>
       </c>
     </row>
@@ -8493,32 +8493,32 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>15,880</t>
+          <t>16,140</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>상승 60</t>
+          <t>상승 320</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+2.02%</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>19,020</t>
+          <t>60,915</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>978</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>6,492</t>
+          <t>6,598</t>
         </is>
       </c>
     </row>
@@ -8535,32 +8535,32 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>17,690</t>
+          <t>17,820</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>상승 350</t>
+          <t>상승 480</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>+2.02%</t>
+          <t>+2.77%</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>33,502</t>
+          <t>79,269</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>1,409</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>6,129</t>
+          <t>6,174</t>
         </is>
       </c>
     </row>
@@ -8577,32 +8577,32 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>117,200</t>
+          <t>122,400</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>하락 3,800</t>
+          <t>상승 1,400</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>-3.14%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>1,993</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>242</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>5,567</t>
+          <t>5,814</t>
         </is>
       </c>
     </row>
@@ -8619,32 +8619,32 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>19,140</t>
+          <t>19,160</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>하락 460</t>
+          <t>하락 440</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-2.24%</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>5,528</t>
+          <t>18,322</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>353</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>5,549</t>
+          <t>5,555</t>
         </is>
       </c>
     </row>
@@ -8661,32 +8661,32 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>103,200</t>
+          <t>104,900</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>하락 3,100</t>
+          <t>하락 1,400</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>-2.92%</t>
+          <t>-1.32%</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>978</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>5,160</t>
+          <t>5,245</t>
         </is>
       </c>
     </row>
@@ -8703,32 +8703,32 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>114,500</t>
+          <t>116,700</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>하락 2,000</t>
+          <t>상승 200</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>-1.72%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2,708</t>
+          <t>10,820</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>1,241</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>4,742</t>
+          <t>4,833</t>
         </is>
       </c>
     </row>
@@ -8745,32 +8745,32 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>10,350</t>
+          <t>10,430</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>하락 530</t>
+          <t>하락 450</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>-4.87%</t>
+          <t>-4.14%</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>17,536</t>
+          <t>65,849</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>688</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>3,975</t>
+          <t>4,006</t>
         </is>
       </c>
     </row>
@@ -8787,32 +8787,32 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>15,140</t>
+          <t>15,110</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>하락 180</t>
+          <t>하락 210</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>24,472</t>
+          <t>77,074</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>1,163</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>3,755</t>
+          <t>3,747</t>
         </is>
       </c>
     </row>
@@ -8829,32 +8829,32 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>170,200</t>
+          <t>171,900</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>하락 6,000</t>
+          <t>하락 4,300</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-3.41%</t>
+          <t>-2.44%</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>4,467</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>764</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>3,504</t>
+          <t>3,539</t>
         </is>
       </c>
     </row>
